--- a/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,491 +656,524 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>5393100</v>
       </c>
       <c r="E8" s="3">
+        <v>5798100</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5377800</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5177400</v>
+      </c>
+      <c r="H8" s="3">
         <v>4810300</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4854600</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>4402000</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>5133700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>4810700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>4572700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>4682200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>5031200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>4473200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>4510700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>4433700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>4331000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>4304600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>4561900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>4474800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="X8" s="3">
         <v>4445500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Y8" s="3">
         <v>4258400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Z8" s="3">
         <v>4261900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AA8" s="3">
         <v>4586100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AB8" s="3">
         <v>5250300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>5208200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>5394500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>5023800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AF8" s="3">
         <v>6138000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AG8" s="3">
         <v>5042300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AH8" s="3">
         <v>6113700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AI8" s="3">
         <v>5489600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AJ8" s="3">
         <v>6037700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AK8" s="3">
         <v>6120900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AL8" s="3">
         <v>6558500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AM8" s="3">
         <v>7162400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AN8" s="3">
         <v>6678100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AO8" s="3">
         <v>6250200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AP8" s="3">
         <v>5616300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>2992600</v>
       </c>
       <c r="E9" s="3">
+        <v>3235100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3128300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2961700</v>
+      </c>
+      <c r="H9" s="3">
         <v>2832500</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2662700</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>2583600</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>3049700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>2692600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>2673800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>2768100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>2887700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>2456800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>2983700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>2816500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>2792900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>2639600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>2863300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>2678900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="X9" s="3">
         <v>2911600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Y9" s="3">
         <v>2651900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Z9" s="3">
         <v>2623600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AA9" s="3">
         <v>2965900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AB9" s="3">
         <v>3323400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AC9" s="3">
         <v>3188900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>3275300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
         <v>2984300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AF9" s="3">
         <v>3960200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AG9" s="3">
         <v>3109200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AH9" s="3">
         <v>3952000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AI9" s="3">
         <v>3459500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AJ9" s="3">
         <v>4148400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AK9" s="3">
         <v>4173600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AL9" s="3">
         <v>4727200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AM9" s="3">
         <v>5316600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AN9" s="3">
         <v>4878500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AO9" s="3">
         <v>4517300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AP9" s="3">
         <v>3914700</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>2400600</v>
       </c>
       <c r="E10" s="3">
+        <v>2563000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2249500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2215700</v>
+      </c>
+      <c r="H10" s="3">
         <v>1977900</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2191900</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
+        <v>1818400</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>2084000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>2118100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>1898900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>1914100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>2143500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>2016400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>1527000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>1617200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>1538100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>1665000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>1698700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>1795800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="X10" s="3">
         <v>1534000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>1606500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>1638300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>1620200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>1926900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>2019300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>2119200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>2039500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AF10" s="3">
         <v>2177800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AG10" s="3">
         <v>1933100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AH10" s="3">
         <v>2161700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AI10" s="3">
         <v>2030100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AJ10" s="3">
         <v>1889300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AK10" s="3">
         <v>1947200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AL10" s="3">
         <v>1831300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AM10" s="3">
         <v>1845700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AN10" s="3">
         <v>1799600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AO10" s="3">
         <v>1732900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AP10" s="3">
         <v>1701600</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1213,11 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1293,8 +1329,17 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1406,234 +1451,261 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-335300</v>
       </c>
       <c r="E14" s="3">
+        <v>469800</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-614100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="H14" s="3">
         <v>-50800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-32900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-395200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="M14" s="3">
         <v>-53900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="N14" s="3">
         <v>-14900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="O14" s="3">
         <v>-5900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="P14" s="3">
         <v>-38100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="Q14" s="3">
         <v>3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="T14" s="3">
         <v>136800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="U14" s="3">
         <v>102900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="X14" s="3">
         <v>13000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Z14" s="3">
         <v>2500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AA14" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AB14" s="3">
         <v>22500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AC14" s="3">
         <v>4700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AF14" s="3">
         <v>23000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AJ14" s="3">
         <v>22600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AK14" s="3">
         <v>14100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AL14" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AM14" s="3">
         <v>9800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AN14" s="3">
         <v>38400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AO14" s="3">
         <v>30100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AP14" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>622600</v>
       </c>
       <c r="E15" s="3">
+        <v>636400</v>
+      </c>
+      <c r="F15" s="3">
+        <v>677400</v>
+      </c>
+      <c r="G15" s="3">
+        <v>692300</v>
+      </c>
+      <c r="H15" s="3">
         <v>667000</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>700800</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>566100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>599700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="M15" s="3">
         <v>674200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
         <v>623400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="O15" s="3">
         <v>590600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="P15" s="3">
         <v>669700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="Q15" s="3">
         <v>15700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="R15" s="3">
         <v>13900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="S15" s="3">
         <v>14600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="T15" s="3">
         <v>15400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="U15" s="3">
         <v>16000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="V15" s="3">
         <v>14800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="W15" s="3">
         <v>17500</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3">
         <v>15100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Z15" s="3">
         <v>16500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AA15" s="3">
         <v>16700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AB15" s="3">
         <v>20100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AC15" s="3">
         <v>17200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
         <v>16400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AE15" s="3">
         <v>16200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AF15" s="3">
         <v>13200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AG15" s="3">
         <v>12500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AH15" s="3">
         <v>10500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AI15" s="3">
         <v>9900</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL15" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AM15" s="3">
         <v>11000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AN15" s="3">
         <v>13300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AO15" s="3">
         <v>11900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AP15" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1670,234 +1742,255 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>4232600</v>
       </c>
       <c r="E17" s="3">
+        <v>4500500</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4210200</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4050700</v>
+      </c>
+      <c r="H17" s="3">
         <v>3949300</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4204000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>3585500</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>4070400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>3858000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>3697900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>3860600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>3656800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>3834400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>4082800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>3868600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>4198400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>3801700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>3790900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>3725200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>3979600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>3717000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>3682900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>4160600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AB17" s="3">
         <v>4960500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AC17" s="3">
         <v>4524800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AD17" s="3">
         <v>4603700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AE17" s="3">
         <v>4330800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AF17" s="3">
         <v>5453200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AG17" s="3">
         <v>4446700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AH17" s="3">
         <v>5155900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AI17" s="3">
         <v>4653400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AJ17" s="3">
         <v>5469000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AK17" s="3">
         <v>5359200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AL17" s="3">
         <v>5681200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AM17" s="3">
         <v>6330900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AN17" s="3">
         <v>5953800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AO17" s="3">
         <v>5529800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AP17" s="3">
         <v>4916200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>1160500</v>
       </c>
       <c r="E18" s="3">
+        <v>1297600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1167600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1126700</v>
+      </c>
+      <c r="H18" s="3">
         <v>861000</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>650600</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>816600</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>1063400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>952700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>874700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>821600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>1374400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>638800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>427900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>565100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>132600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>502900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>771000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>749500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>465900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>541400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>579000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>425500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>289800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>683400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>790800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AE18" s="3">
         <v>693000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AF18" s="3">
         <v>684800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AG18" s="3">
         <v>595600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AH18" s="3">
         <v>957800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AI18" s="3">
         <v>836200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AJ18" s="3">
         <v>568700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AK18" s="3">
         <v>761700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AL18" s="3">
         <v>877300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AM18" s="3">
         <v>831500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AN18" s="3">
         <v>724300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AO18" s="3">
         <v>720400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AP18" s="3">
         <v>700100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1937,276 +2030,297 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-1279100</v>
       </c>
       <c r="E20" s="3">
+        <v>-260600</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-140700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-134700</v>
+      </c>
+      <c r="H20" s="3">
         <v>-35400</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-541700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>73000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>-222800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>-67000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>-88700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>320600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>212500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="R20" s="3">
         <v>86100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="S20" s="3">
         <v>11600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>1117000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>155900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>99500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>-14100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="X20" s="3">
         <v>87000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Y20" s="3">
         <v>11300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>-60600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AA20" s="3">
         <v>151400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AB20" s="3">
         <v>257300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AC20" s="3">
         <v>426400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AD20" s="3">
         <v>401800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AE20" s="3">
         <v>212600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AF20" s="3">
         <v>281600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AG20" s="3">
         <v>105100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AH20" s="3">
         <v>64000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AI20" s="3">
         <v>172300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AJ20" s="3">
         <v>109400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AK20" s="3">
         <v>213500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AL20" s="3">
         <v>180400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AM20" s="3">
         <v>394400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AN20" s="3">
         <v>81700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AO20" s="3">
         <v>298400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AP20" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>3062200</v>
       </c>
       <c r="E21" s="3">
+        <v>2194700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1985600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1953700</v>
+      </c>
+      <c r="H21" s="3">
         <v>1563400</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1893100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>1430900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>1590000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>1849600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <v>1565100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>1501000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>1723600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>1512500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="R21" s="3">
         <v>1056900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>1130600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>1804400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>1225900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>1465700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>1335800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="X21" s="3">
         <v>1121400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Y21" s="3">
         <v>1144900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Z21" s="3">
         <v>1126200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AA21" s="3">
         <v>1233300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AB21" s="3">
         <v>1255100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AC21" s="3">
         <v>1783600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AD21" s="3">
         <v>1888900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AE21" s="3">
         <v>1584500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AF21" s="3">
         <v>1712100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AG21" s="3">
         <v>1406800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AH21" s="3">
         <v>1694300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AI21" s="3">
         <v>1652200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AJ21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AK21" s="3">
         <v>1600300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AL21" s="3">
         <v>1668200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AM21" s="3">
         <v>1822700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AN21" s="3">
         <v>1389400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AO21" s="3">
         <v>1580800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AP21" s="3">
         <v>1445600</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>276200</v>
       </c>
       <c r="E22" s="3">
+        <v>310400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>327600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>287700</v>
+      </c>
+      <c r="H22" s="3">
         <v>298900</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>270200</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>279800</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>327900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>338700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="N22" s="3">
         <v>320100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="O22" s="3">
         <v>298000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="P22" s="3">
         <v>293400</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2276,234 +2390,261 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>2498700</v>
       </c>
       <c r="E23" s="3">
+        <v>778000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1594700</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1009600</v>
+      </c>
+      <c r="H23" s="3">
         <v>648300</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>955000</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>747000</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>1057600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>890600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>636500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>618300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>798500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>851300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>514000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>576700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>1249600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>658800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>870500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>735400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>552900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>552700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>518400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AA23" s="3">
         <v>576900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AB23" s="3">
         <v>547100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>1109900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>1192600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AE23" s="3">
         <v>905600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AF23" s="3">
         <v>966400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AG23" s="3">
         <v>700700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AH23" s="3">
         <v>1021800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AI23" s="3">
         <v>1008600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AJ23" s="3">
         <v>678100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AK23" s="3">
         <v>975200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AL23" s="3">
         <v>1057700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AM23" s="3">
         <v>1225900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AN23" s="3">
         <v>806000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AO23" s="3">
         <v>1018800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AP23" s="3">
         <v>894100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
+      <c r="D24" s="3">
+        <v>772600</v>
       </c>
       <c r="E24" s="3">
+        <v>382400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>475800</v>
+      </c>
+      <c r="G24" s="3">
+        <v>299600</v>
+      </c>
+      <c r="H24" s="3">
         <v>114500</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>278200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>217600</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>257900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>273500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>191400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>174500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>198700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="Q24" s="3">
         <v>204900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="R24" s="3">
         <v>119700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="S24" s="3">
         <v>143000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="T24" s="3">
         <v>574000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="U24" s="3">
         <v>226000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="V24" s="3">
         <v>278400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
         <v>216500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="X24" s="3">
         <v>179500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Y24" s="3">
         <v>187500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Z24" s="3">
         <v>167500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AA24" s="3">
         <v>146500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AB24" s="3">
         <v>86600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AC24" s="3">
         <v>325100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AD24" s="3">
         <v>349300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AE24" s="3">
         <v>265200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AF24" s="3">
         <v>120600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AG24" s="3">
         <v>-77300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AH24" s="3">
         <v>310300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AI24" s="3">
         <v>281100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AJ24" s="3">
         <v>135400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AK24" s="3">
         <v>142100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AL24" s="3">
         <v>348400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AM24" s="3">
         <v>403800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AN24" s="3">
         <v>300000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AO24" s="3">
         <v>336300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AP24" s="3">
         <v>295100</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2615,234 +2756,261 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>1726100</v>
       </c>
       <c r="E26" s="3">
+        <v>395700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="G26" s="3">
+        <v>710100</v>
+      </c>
+      <c r="H26" s="3">
         <v>533800</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>676800</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>529400</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>799700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>617100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>445100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>443700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>599900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>646400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>394200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>433700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>675600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>432900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>592100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>518900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="X26" s="3">
         <v>373300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>365200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Z26" s="3">
         <v>350800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AA26" s="3">
         <v>430400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>460500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>784800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>843300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AE26" s="3">
         <v>640300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AF26" s="3">
         <v>845800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AG26" s="3">
         <v>777900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AH26" s="3">
         <v>711500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AI26" s="3">
         <v>727500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AJ26" s="3">
         <v>542700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AK26" s="3">
         <v>833100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AL26" s="3">
         <v>709300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AM26" s="3">
         <v>822100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AN26" s="3">
         <v>506000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AO26" s="3">
         <v>682500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AP26" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>1727700</v>
       </c>
       <c r="E27" s="3">
+        <v>361600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1106600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>743600</v>
+      </c>
+      <c r="H27" s="3">
         <v>533000</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>671500</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>539200</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>839100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>646300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>436100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>435500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>589900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>636200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>385300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>417400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>668300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>444200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>587400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>479300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="X27" s="3">
         <v>365300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Y27" s="3">
         <v>353100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Z27" s="3">
         <v>341200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AA27" s="3">
         <v>426900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>455800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>775900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>826500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AE27" s="3">
         <v>634000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AF27" s="3">
         <v>841200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AG27" s="3">
         <v>766100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AH27" s="3">
         <v>697700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AI27" s="3">
         <v>726700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AJ27" s="3">
         <v>513000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AK27" s="3">
         <v>817400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AL27" s="3">
         <v>689400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AM27" s="3">
         <v>811000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AN27" s="3">
         <v>497800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AO27" s="3">
         <v>665000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AP27" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2954,13 +3122,22 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>27100</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2969,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
+        <v>47300</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2989,86 +3166,95 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>900</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-8200</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>58500</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3180,8 +3366,17 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3293,234 +3488,261 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>1279100</v>
       </c>
       <c r="E32" s="3">
+        <v>260600</v>
+      </c>
+      <c r="F32" s="3">
+        <v>140700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>134700</v>
+      </c>
+      <c r="H32" s="3">
         <v>35400</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>541700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>48200</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-73000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>222800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>67000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>88700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>-320600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>-212500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="R32" s="3">
         <v>-86100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="S32" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>-1117000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>-155900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>-99500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>14100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="X32" s="3">
         <v>-87000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Y32" s="3">
         <v>-11300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Z32" s="3">
         <v>60600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AA32" s="3">
         <v>-151400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AB32" s="3">
         <v>-257300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AC32" s="3">
         <v>-426400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AD32" s="3">
         <v>-401800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AE32" s="3">
         <v>-212600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AF32" s="3">
         <v>-281600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AG32" s="3">
         <v>-105100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AH32" s="3">
         <v>-64000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AI32" s="3">
         <v>-172300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AJ32" s="3">
         <v>-109400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AK32" s="3">
         <v>-213500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AL32" s="3">
         <v>-180400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AM32" s="3">
         <v>-394400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AN32" s="3">
         <v>-81700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AO32" s="3">
         <v>-298400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AP32" s="3">
         <v>-194000</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>1727700</v>
       </c>
       <c r="E33" s="3">
+        <v>362200</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1106900</v>
+      </c>
+      <c r="G33" s="3">
+        <v>743600</v>
+      </c>
+      <c r="H33" s="3">
         <v>533200</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>671600</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>539200</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>839200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>646300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>436100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>435500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>589900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>636200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>385300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>417400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>669300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>444200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>587400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>479300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="X33" s="3">
         <v>357100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Y33" s="3">
         <v>353100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Z33" s="3">
         <v>341200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AA33" s="3">
         <v>426900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>514300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>775900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>826500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AE33" s="3">
         <v>634000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AF33" s="3">
         <v>841200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AG33" s="3">
         <v>766100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AH33" s="3">
         <v>697700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AI33" s="3">
         <v>726700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AJ33" s="3">
         <v>513000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AK33" s="3">
         <v>817400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AL33" s="3">
         <v>689400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AM33" s="3">
         <v>811000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AN33" s="3">
         <v>497800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AO33" s="3">
         <v>665000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AP33" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3632,239 +3854,266 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>1727700</v>
       </c>
       <c r="E35" s="3">
+        <v>362200</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1106900</v>
+      </c>
+      <c r="G35" s="3">
+        <v>743600</v>
+      </c>
+      <c r="H35" s="3">
         <v>533200</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>671600</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>539200</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>839200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>646300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>436100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>435500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>589900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>636200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>385300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>417400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>669300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>444200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>587400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="W35" s="3">
         <v>479300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="X35" s="3">
         <v>357100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Y35" s="3">
         <v>353100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Z35" s="3">
         <v>341200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AA35" s="3">
         <v>426900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>514300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>775900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>826500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AE35" s="3">
         <v>634000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AF35" s="3">
         <v>841200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AG35" s="3">
         <v>766100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AH35" s="3">
         <v>697700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AI35" s="3">
         <v>726700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AJ35" s="3">
         <v>513000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AK35" s="3">
         <v>817400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AL35" s="3">
         <v>689400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AM35" s="3">
         <v>811000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AN35" s="3">
         <v>497800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AO35" s="3">
         <v>665000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AP35" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3904,8 +4153,11 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3945,121 +4197,133 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>8</v>
+      <c r="D41" s="3">
+        <v>5961000</v>
       </c>
       <c r="E41" s="3">
+        <v>8395600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8621700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>8363600</v>
+      </c>
+      <c r="H41" s="3">
         <v>8057400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8159400</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>6171300</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3">
         <v>6828300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>6415100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>6126800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>6378400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>9266700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>7575800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>6673600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>6706200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>7249600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>7084100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>8377200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>8349700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>7654200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>8305200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>10183900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>10067500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>10001900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AC41" s="3">
         <v>9297700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AD41" s="3">
         <v>10195800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AE41" s="3">
         <v>10468300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AF41" s="3">
         <v>12335200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AG41" s="3">
         <v>12604300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AH41" s="3">
         <v>11656800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AI41" s="3">
         <v>12061800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AJ41" s="3">
         <v>12702300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AK41" s="3">
         <v>11964900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AL41" s="3">
         <v>11518800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AM41" s="3">
         <v>11731700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AN41" s="3">
         <v>10051600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AO41" s="3">
         <v>9284500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AP41" s="3">
         <v>9275800</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4067,41 +4331,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>177900</v>
+      </c>
+      <c r="F42" s="3">
+        <v>156800</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>128700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>126600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>139000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>198100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>226300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>213000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>220800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4171,276 +4435,303 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>19490300</v>
       </c>
       <c r="E43" s="3">
+        <v>37177900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>39156400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>38963200</v>
+      </c>
+      <c r="H43" s="3">
         <v>37921600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>37039000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
+        <v>33602900</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>36640000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>38203900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>36401600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>37888900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>40837100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>2136000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>1849700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>2251200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>1928900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>1578100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>1519400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>1779900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>1952500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>1566800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>1312300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AA43" s="3">
         <v>1704500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AB43" s="3">
         <v>2254500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AC43" s="3">
         <v>1999500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AD43" s="3">
         <v>1879200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AE43" s="3">
         <v>2136800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AF43" s="3">
         <v>2139000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AG43" s="3">
         <v>1930100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AH43" s="3">
         <v>2040800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AI43" s="3">
         <v>2255700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AJ43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AK43" s="3">
         <v>2281800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AL43" s="3">
         <v>1973500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AM43" s="3">
         <v>1850500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AN43" s="3">
         <v>1988700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AO43" s="3">
         <v>1868400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AP43" s="3">
         <v>1833400</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>1670700</v>
       </c>
       <c r="E44" s="3">
+        <v>1692900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1624300</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1488300</v>
+      </c>
+      <c r="H44" s="3">
         <v>1530800</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1514100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>1351500</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>1503200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>1640100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>1492400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>1175900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>1271500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>1036000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>986100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>987100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>926700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>948200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>958100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>1006200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>1007900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>1080000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>1053500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AA44" s="3">
         <v>1105000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AB44" s="3">
         <v>1110200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AC44" s="3">
         <v>1202100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AD44" s="3">
         <v>1161000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AE44" s="3">
         <v>1146700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AF44" s="3">
         <v>1111800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AG44" s="3">
         <v>1369000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AH44" s="3">
         <v>1220500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AI44" s="3">
         <v>1117200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AJ44" s="3">
         <v>1003400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AK44" s="3">
         <v>1246700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AL44" s="3">
         <v>1174100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AM44" s="3">
         <v>1116500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AN44" s="3">
         <v>1045400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AO44" s="3">
         <v>1265400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AP44" s="3">
         <v>1328700</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>20068500</v>
       </c>
       <c r="E45" s="3">
+        <v>806000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>447300</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>309200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>341300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>357000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>384100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>495400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>708000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>373100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4510,50 +4801,59 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>8</v>
+      <c r="D46" s="3">
+        <v>47945300</v>
       </c>
       <c r="E46" s="3">
+        <v>48980800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>50816100</v>
+      </c>
+      <c r="G46" s="3">
+        <v>49615300</v>
+      </c>
+      <c r="H46" s="3">
         <v>48718300</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>48120300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
+        <v>42144800</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
         <v>46475600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>47840200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>45673900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>47320300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>52985100</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4623,299 +4923,326 @@
       <c r="AM46" s="3">
         <v>0</v>
       </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>28782400</v>
       </c>
       <c r="E47" s="3">
-        <v>29531300</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
+        <v>28193000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>30359600</v>
       </c>
       <c r="G47" s="3">
+        <v>31923800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>29493700</v>
+      </c>
+      <c r="I47" s="3">
         <v>30723000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
+        <v>28805900</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>29193900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>30071400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>27829000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>28075100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>28293500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>55010700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="R47" s="3">
         <v>51027800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="S47" s="3">
         <v>53430500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="T47" s="3">
         <v>51081400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="U47" s="3">
         <v>52315800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="V47" s="3">
         <v>52503500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="W47" s="3">
         <v>52973200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="X47" s="3">
         <v>51182600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Y47" s="3">
         <v>51463300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Z47" s="3">
         <v>53541500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AA47" s="3">
         <v>58386100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AB47" s="3">
         <v>59973800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AC47" s="3">
         <v>74441200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AD47" s="3">
         <v>71989200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AE47" s="3">
         <v>69844300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AF47" s="3">
         <v>82078400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AG47" s="3">
         <v>78817700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AH47" s="3">
         <v>75266400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AI47" s="3">
         <v>69855700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AJ47" s="3">
         <v>69467000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AK47" s="3">
         <v>71014900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AL47" s="3">
         <v>70684000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AM47" s="3">
         <v>70420000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AN47" s="3">
         <v>69927900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AO47" s="3">
         <v>70281800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AP47" s="3">
         <v>67221000</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>5681100</v>
       </c>
       <c r="E48" s="3">
+        <v>6611600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6487400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6585000</v>
+      </c>
+      <c r="H48" s="3">
         <v>6927100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6569600</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>5910300</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3">
         <v>6779200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>6461400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>5943500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>6094500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>7319900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>16212000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>14530600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>15370200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>15042700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>15489200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="V48" s="3">
         <v>16390700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="W48" s="3">
         <v>15748800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="X48" s="3">
         <v>15218300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Y48" s="3">
         <v>16071400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>16625000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AA48" s="3">
         <v>18395500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>19086100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AC48" s="3">
         <v>6587600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AD48" s="3">
         <v>6033700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AE48" s="3">
         <v>6371700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AF48" s="3">
         <v>5285700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AG48" s="3">
         <v>5647800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AH48" s="3">
         <v>5234600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AI48" s="3">
         <v>5009900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AJ48" s="3">
         <v>4951600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AK48" s="3">
         <v>4682600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AL48" s="3">
         <v>4655100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AM48" s="3">
         <v>4632500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AN48" s="3">
         <v>4521200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AO48" s="3">
         <v>4311900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AP48" s="3">
         <v>4267300</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>9006500</v>
+      </c>
+      <c r="F49" s="3">
+        <v>9533200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>8171900</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8517000</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3">
         <v>8227500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>8927300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>8608000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>8806500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>9163100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>6633600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>6103600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>6015300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4962,8 +5289,17 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5075,8 +5411,17 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5188,50 +5533,59 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>29907300</v>
       </c>
       <c r="E52" s="3">
-        <v>18859400</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
+        <v>20133100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>21760400</v>
       </c>
       <c r="G52" s="3">
+        <v>29707500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>18896900</v>
+      </c>
+      <c r="I52" s="3">
         <v>20125100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
+        <v>25723600</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>16795200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>16449000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>15698900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>15455000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>16890000</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5301,8 +5655,17 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5414,121 +5777,139 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>8</v>
+      <c r="D54" s="3">
+        <v>112316100</v>
       </c>
       <c r="E54" s="3">
+        <v>113221400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>118956700</v>
+      </c>
+      <c r="G54" s="3">
+        <v>117831700</v>
+      </c>
+      <c r="H54" s="3">
         <v>112630900</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>114055000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>102584500</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
         <v>107911100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>111868400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>105751300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>107785400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>115014900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>103332600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>94334700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>98555600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>94757300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>96806300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>99748000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>99827500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>96162300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>97668500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>102579300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AA54" s="3">
         <v>111679100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AB54" s="3">
         <v>115124900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AC54" s="3">
         <v>116999300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AD54" s="3">
         <v>114976800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AE54" s="3">
         <v>113629300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AF54" s="3">
         <v>117001000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AG54" s="3">
         <v>114429700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AH54" s="3">
         <v>109422700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AI54" s="3">
         <v>103370600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AJ54" s="3">
         <v>103290900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AK54" s="3">
         <v>104429300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AL54" s="3">
         <v>103291400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AM54" s="3">
         <v>102314200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AN54" s="3">
         <v>99626900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AO54" s="3">
         <v>98834300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AP54" s="3">
         <v>95642500</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5568,8 +5949,11 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5609,389 +5993,419 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>2003700</v>
       </c>
       <c r="E57" s="3">
+        <v>2239000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2143400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2182800</v>
+      </c>
+      <c r="H57" s="3">
         <v>2269100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2075400</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>2008500</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>2396600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>2345000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>2208300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>2178600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>2759600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>1794600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>1585600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>1774500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>1935000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>1556000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="V57" s="3">
         <v>1660300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="W57" s="3">
         <v>1546400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="X57" s="3">
         <v>1848400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Y57" s="3">
         <v>1558500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Z57" s="3">
         <v>1535100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AA57" s="3">
         <v>1627400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AB57" s="3">
         <v>2490800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AC57" s="3">
         <v>2067100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AD57" s="3">
         <v>2140100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AE57" s="3">
         <v>2032100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AF57" s="3">
         <v>2820300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AG57" s="3">
         <v>2206000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AH57" s="3">
         <v>2131700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AI57" s="3">
         <v>2416200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AJ57" s="3">
         <v>2371200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AK57" s="3">
         <v>1898700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AL57" s="3">
         <v>1915700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AM57" s="3">
         <v>1891500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AN57" s="3">
         <v>2233500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AO57" s="3">
         <v>1846800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AP57" s="3">
         <v>1846700</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>3584700</v>
       </c>
       <c r="E58" s="3">
-        <v>9838800</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
+        <v>10461200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>4140300</v>
       </c>
       <c r="G58" s="3">
+        <v>4366000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3689200</v>
+      </c>
+      <c r="I58" s="3">
         <v>5220900</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>3991300</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3">
         <v>3820200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>4615500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>3947200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>4005700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>3852400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>3163300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>2945500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="S58" s="3">
         <v>3984500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="T58" s="3">
         <v>2919200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>4574600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="V58" s="3">
         <v>3561600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="W58" s="3">
         <v>3355000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="X58" s="3">
         <v>2178500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Y58" s="3">
         <v>2722800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Z58" s="3">
         <v>2816300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AA58" s="3">
         <v>3217100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AB58" s="3">
         <v>2967500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AC58" s="3">
         <v>3499400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AD58" s="3">
         <v>2525500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AE58" s="3">
         <v>3084300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AF58" s="3">
         <v>2974800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AG58" s="3">
         <v>6124400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AH58" s="3">
         <v>3014300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AI58" s="3">
         <v>2165000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AJ58" s="3">
         <v>2773100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AK58" s="3">
         <v>3241500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AL58" s="3">
         <v>3034400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AM58" s="3">
         <v>3398100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AN58" s="3">
         <v>2514400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AO58" s="3">
         <v>2628100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AP58" s="3">
         <v>1852200</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>22991600</v>
       </c>
       <c r="E59" s="3">
-        <v>10444200</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
+        <v>12825000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5045800</v>
       </c>
       <c r="G59" s="3">
+        <v>4183800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>710600</v>
+      </c>
+      <c r="I59" s="3">
         <v>4414400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>3381700</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>1041200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>4082900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>3918700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>4363600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>701400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>18750000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>16383500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>17574500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>20002500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>18559000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>19455100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="W59" s="3">
         <v>19718700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="X59" s="3">
         <v>21080400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
         <v>19858200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Z59" s="3">
         <v>20846200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AA59" s="3">
         <v>22491300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AB59" s="3">
         <v>22800700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AC59" s="3">
         <v>23138900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AD59" s="3">
         <v>22619100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AE59" s="3">
         <v>21575000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AF59" s="3">
         <v>21945200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AG59" s="3">
         <v>21264700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AH59" s="3">
         <v>21021000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AI59" s="3">
         <v>19682100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AJ59" s="3">
         <v>19204700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AK59" s="3">
         <v>19329900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AL59" s="3">
         <v>19044800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AM59" s="3">
         <v>18495000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AN59" s="3">
         <v>18275000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AO59" s="3">
         <v>17244500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AP59" s="3">
         <v>16647500</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>8</v>
+      <c r="D60" s="3">
+        <v>28580000</v>
       </c>
       <c r="E60" s="3">
-        <v>22552000</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>8</v>
+        <v>25525100</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11329500</v>
       </c>
       <c r="G60" s="3">
+        <v>10732600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6668900</v>
+      </c>
+      <c r="I60" s="3">
         <v>11710800</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>9381600</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>7258100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>11043400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>10074300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>10547800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>7313500</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6061,163 +6475,181 @@
       <c r="AM60" s="3">
         <v>0</v>
       </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>35227900</v>
       </c>
       <c r="E61" s="3">
-        <v>33867400</v>
+        <v>32612400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>39945300</v>
       </c>
       <c r="G61" s="3">
+        <v>39863300</v>
+      </c>
+      <c r="H61" s="3">
+        <v>40016900</v>
+      </c>
+      <c r="I61" s="3">
         <v>38353200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>35703700</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>38918400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>37838000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>36476800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>36489700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>41356500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>33794000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="R61" s="3">
         <v>31572800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="S61" s="3">
         <v>31785500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>29446700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>29889600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="V61" s="3">
         <v>31374300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="W61" s="3">
         <v>31744800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="X61" s="3">
         <v>31339600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Y61" s="3">
         <v>31786500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Z61" s="3">
         <v>33212400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AA61" s="3">
         <v>37004500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AB61" s="3">
         <v>37701100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AC61" s="3">
         <v>37525700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AD61" s="3">
         <v>37410700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AE61" s="3">
         <v>37668500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AF61" s="3">
         <v>40229600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AG61" s="3">
         <v>37481900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AH61" s="3">
         <v>35869000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AI61" s="3">
         <v>34202200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AJ61" s="3">
         <v>34591600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AK61" s="3">
         <v>35174700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AL61" s="3">
         <v>34962700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AM61" s="3">
         <v>35088200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AN61" s="3">
         <v>34193700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AO61" s="3">
         <v>34384900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AP61" s="3">
         <v>33751200</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>18716000</v>
       </c>
       <c r="E62" s="3">
-        <v>24436600</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
+        <v>21767100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>36553100</v>
       </c>
       <c r="G62" s="3">
+        <v>37938700</v>
+      </c>
+      <c r="H62" s="3">
+        <v>34170200</v>
+      </c>
+      <c r="I62" s="3">
         <v>35953600</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
+        <v>31643700</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>31453900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>35752500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>33269900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>34787700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>35535300</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6287,8 +6719,17 @@
       <c r="AM62" s="3">
         <v>0</v>
       </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6400,8 +6841,17 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6513,8 +6963,17 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6626,121 +7085,139 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>8</v>
+      <c r="D66" s="3">
+        <v>82523900</v>
       </c>
       <c r="E66" s="3">
+        <v>84141800</v>
+      </c>
+      <c r="F66" s="3">
+        <v>88075700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>88534600</v>
+      </c>
+      <c r="H66" s="3">
         <v>84749300</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>86264300</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
+        <v>76729000</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
         <v>81303000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>84862100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>80016200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>82031300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>87818900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>80219200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>72994800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>76355800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>73101400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>75179800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>77269700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>77428100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>74690500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>76131100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>79367500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>86642100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>88751200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AC66" s="3">
         <v>89592700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AD66" s="3">
         <v>87755300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AE66" s="3">
         <v>87183700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AF66" s="3">
         <v>89160100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AG66" s="3">
         <v>87832500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AH66" s="3">
         <v>83373800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AI66" s="3">
         <v>78716600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AJ66" s="3">
         <v>79041800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AK66" s="3">
         <v>80311500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AL66" s="3">
         <v>79690300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AM66" s="3">
         <v>79485200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AN66" s="3">
         <v>77383600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AO66" s="3">
         <v>77218100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AP66" s="3">
         <v>74665300</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6780,8 +7257,11 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6893,8 +7373,17 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7006,8 +7495,17 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7119,8 +7617,17 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7232,121 +7739,139 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>22853200</v>
       </c>
       <c r="E72" s="3">
+        <v>22027700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>24056400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>23540200</v>
+      </c>
+      <c r="H72" s="3">
         <v>22403700</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>23579600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>20401500</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>21551200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>22515000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>20971500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>21213900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>22977200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>21402300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>18983000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>19650300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>19317900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>19625900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>20469500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>20268200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>19459100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>20219500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>21453300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AA72" s="3">
         <v>23117700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AB72" s="3">
         <v>24266800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AC72" s="3">
         <v>24561300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AD72" s="3">
         <v>24406600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AE72" s="3">
         <v>23503000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AF72" s="3">
         <v>24559200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AG72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AH72" s="3">
         <v>22550800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AI72" s="3">
         <v>21382600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AJ72" s="3">
         <v>20930200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AK72" s="3">
         <v>20440400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AL72" s="3">
         <v>19935700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AM72" s="3">
         <v>19246400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AN72" s="3">
         <v>18427200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AO72" s="3">
         <v>17917900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AP72" s="3">
         <v>17520500</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7458,8 +7983,17 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7571,8 +8105,17 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7684,121 +8227,139 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>8</v>
+      <c r="D76" s="3">
+        <v>28979200</v>
       </c>
       <c r="E76" s="3">
+        <v>28190900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>30013600</v>
+      </c>
+      <c r="G76" s="3">
+        <v>28733200</v>
+      </c>
+      <c r="H76" s="3">
         <v>27311100</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>27237800</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
+        <v>25323200</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" s="3">
         <v>26058400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>26442600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>25181100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>25198400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>26656900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>23113400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>21339900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>22199700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>21655800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>21626500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>22478300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>22399400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>21471800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>21537500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>23211700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>25037000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>26373700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AC76" s="3">
         <v>27406600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AD76" s="3">
         <v>27221500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AE76" s="3">
         <v>26445600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AF76" s="3">
         <v>27840900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AG76" s="3">
         <v>26597200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AH76" s="3">
         <v>26048900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AI76" s="3">
         <v>24653900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AJ76" s="3">
         <v>24249100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AK76" s="3">
         <v>24117900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AL76" s="3">
         <v>23601100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AM76" s="3">
         <v>22829000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AN76" s="3">
         <v>22243300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AO76" s="3">
         <v>21616300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AP76" s="3">
         <v>20977200</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7910,239 +8471,266 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>1727700</v>
       </c>
       <c r="E81" s="3">
+        <v>362200</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1106900</v>
+      </c>
+      <c r="G81" s="3">
+        <v>743600</v>
+      </c>
+      <c r="H81" s="3">
         <v>533200</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>671600</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>539200</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>839200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>646300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>436100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>435500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>589900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>636200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>385300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>417400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>669300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>444200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>587400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="W81" s="3">
         <v>479300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="X81" s="3">
         <v>357100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Y81" s="3">
         <v>353100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Z81" s="3">
         <v>341200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AA81" s="3">
         <v>426900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>514300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>775900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>826500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AE81" s="3">
         <v>634000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AF81" s="3">
         <v>841200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AG81" s="3">
         <v>766100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AH81" s="3">
         <v>697700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AI81" s="3">
         <v>726700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AJ81" s="3">
         <v>513000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AK81" s="3">
         <v>817400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AL81" s="3">
         <v>689400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AM81" s="3">
         <v>811000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AN81" s="3">
         <v>497800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AO81" s="3">
         <v>665000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AP81" s="3">
         <v>579900</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8182,121 +8770,133 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>340400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>674200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>623400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>590600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
+        <v>590600</v>
+      </c>
+      <c r="L83" s="3">
         <v>412400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>687800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>561400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>583400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>688200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>661200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="R83" s="3">
         <v>543000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="S83" s="3">
         <v>553900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="T83" s="3">
         <v>554900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="U83" s="3">
         <v>567100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="V83" s="3">
         <v>595200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="W83" s="3">
         <v>600400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="X83" s="3">
         <v>568500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Y83" s="3">
         <v>592200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Z83" s="3">
         <v>607800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="AA83" s="3">
         <v>656400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AB83" s="3">
         <v>708000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AC83" s="3">
         <v>673700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AD83" s="3">
         <v>696300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AE83" s="3">
         <v>678900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AF83" s="3">
         <v>745700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AG83" s="3">
         <v>706100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AH83" s="3">
         <v>672500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AI83" s="3">
         <v>643600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AJ83" s="3">
         <v>698100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AK83" s="3">
         <v>625100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AL83" s="3">
         <v>610500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AM83" s="3">
         <v>596800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AN83" s="3">
         <v>583400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AO83" s="3">
         <v>562000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AP83" s="3">
         <v>551500</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8408,8 +9008,17 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8521,8 +9130,17 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8634,8 +9252,17 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8747,8 +9374,17 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8860,8 +9496,17 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8880,101 +9525,110 @@
       <c r="H89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>2094600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>2380500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>2638800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>1361800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>2508500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>2248700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>1879900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>-214000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>2243300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>1184200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>2698700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="W89" s="3">
         <v>1608600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="X89" s="3">
         <v>2407900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Y89" s="3">
         <v>1732000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Z89" s="3">
         <v>2631100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AA89" s="3">
         <v>1552600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AB89" s="3">
         <v>2834900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AC89" s="3">
         <v>1711200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AD89" s="3">
         <v>3255200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AE89" s="3">
         <v>1636300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AF89" s="3">
         <v>1980300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AG89" s="3">
         <v>1020200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AH89" s="3">
         <v>1637600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AI89" s="3">
         <v>884100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AJ89" s="3">
         <v>1772000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AK89" s="3">
         <v>1193700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AL89" s="3">
         <v>1172300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AM89" s="3">
         <v>803500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AN89" s="3">
         <v>1250000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AO89" s="3">
         <v>994000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AP89" s="3">
         <v>1888000</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9014,8 +9668,11 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9034,101 +9691,110 @@
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1657000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-2075200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-2252700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-2221800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-2280700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-254596000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-254596000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="S91" s="3">
         <v>-223427000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="T91" s="3">
         <v>-248094000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="U91" s="3">
         <v>-229768000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="V91" s="3">
         <v>-256101000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="W91" s="3">
         <v>-39500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="X91" s="3">
         <v>-42700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Y91" s="3">
         <v>-84600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Z91" s="3">
         <v>-133300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="AA91" s="3">
         <v>-79200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AB91" s="3">
         <v>-172200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AC91" s="3">
         <v>-116600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AD91" s="3">
         <v>-62600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AE91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AF91" s="3">
         <v>-106500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AG91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AH91" s="3">
         <v>-198600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AI91" s="3">
         <v>-147500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AJ91" s="3">
         <v>-155900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AK91" s="3">
         <v>-197500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AL91" s="3">
         <v>-222200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AM91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AN91" s="3">
         <v>-2642900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AO91" s="3">
         <v>-2149200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AP91" s="3">
         <v>-2170900</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9240,8 +9906,17 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9353,8 +10028,17 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9373,101 +10057,110 @@
       <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1041600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-2521100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-3014300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-2833300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-3059900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-1783200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-1362800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-1529700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="T94" s="3">
         <v>-236300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="U94" s="3">
         <v>-2314500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="V94" s="3">
         <v>-2310200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="W94" s="3">
         <v>-852200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="X94" s="3">
         <v>-2514400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Y94" s="3">
         <v>-3140600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Z94" s="3">
         <v>-1425100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AA94" s="3">
         <v>-2023400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AB94" s="3">
         <v>-3372700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AC94" s="3">
         <v>-3499800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AD94" s="3">
         <v>-3389900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AE94" s="3">
         <v>-3065100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AF94" s="3">
         <v>-1698000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AG94" s="3">
         <v>-3863100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AH94" s="3">
         <v>-2709000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AI94" s="3">
         <v>32500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AJ94" s="3">
         <v>-760600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AK94" s="3">
         <v>-1359900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AL94" s="3">
         <v>-1717000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AM94" s="3">
         <v>116900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AN94" s="3">
         <v>-1077700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AO94" s="3">
         <v>-1208800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AP94" s="3">
         <v>-357200</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9507,8 +10200,11 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9527,101 +10223,110 @@
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>352500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>347300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-359200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-375400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-322600</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-385400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-320100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-439200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-408700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-540100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-363000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-454400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-312700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-345000</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-267500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9733,8 +10438,17 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9846,8 +10560,17 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9959,8 +10682,17 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9979,214 +10711,232 @@
       <c r="H100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-217400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>128100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>286700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-784900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>2776100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-190100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-271200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="S100" s="3">
         <v>933800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="T100" s="3">
         <v>-1715900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="U100" s="3">
         <v>192400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="V100" s="3">
         <v>-205900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="W100" s="3">
         <v>-350200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="X100" s="3">
         <v>-356000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Y100" s="3">
         <v>131600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Z100" s="3">
         <v>-216700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AA100" s="3">
         <v>852700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AB100" s="3">
         <v>1587500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AC100" s="3">
         <v>927700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AD100" s="3">
         <v>-136900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AE100" s="3">
         <v>197600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AF100" s="3">
         <v>-769700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AG100" s="3">
         <v>3671900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AH100" s="3">
         <v>352000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AI100" s="3">
         <v>-1637300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AJ100" s="3">
         <v>-330300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AK100" s="3">
         <v>571200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AL100" s="3">
         <v>434300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AM100" s="3">
         <v>622800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AN100" s="3">
         <v>713600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AO100" s="3">
         <v>-108100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AP100" s="3">
         <v>-426900</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>91300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-52300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>47100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>136900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
+        <v>136900</v>
+      </c>
+      <c r="L101" s="3">
         <v>31200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-134900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>86300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>171700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>138400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>-126300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>79700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="S101" s="3">
         <v>157300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="T101" s="3">
         <v>111600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="U101" s="3">
         <v>39900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="W101" s="3">
         <v>8600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="X101" s="3">
         <v>83400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AB101" s="3">
         <v>-39400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AC101" s="3">
         <v>51700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AD101" s="3">
         <v>-35300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AE101" s="3">
         <v>-58100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AF101" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AG101" s="3">
         <v>-69800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AH101" s="3">
         <v>49100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AI101" s="3">
         <v>10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AJ101" s="3">
         <v>-82800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AK101" s="3">
         <v>24000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AL101" s="3">
         <v>42100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AM101" s="3">
         <v>41400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AN101" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AO101" s="3">
         <v>141000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AP101" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10206,96 +10956,105 @@
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>927000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-64800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-41800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-2119500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>2255900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>149100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>325600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>-652600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="T102" s="3">
         <v>402700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="U102" s="3">
         <v>-898100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="V102" s="3">
         <v>186600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="W102" s="3">
         <v>414800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="X102" s="3">
         <v>-379100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Y102" s="3">
         <v>-1277400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Z102" s="3">
         <v>989800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AA102" s="3">
         <v>383500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AB102" s="3">
         <v>1010300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AC102" s="3">
         <v>-809300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AD102" s="3">
         <v>-306900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AE102" s="3">
         <v>-1289300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AF102" s="3">
         <v>-496100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AG102" s="3">
         <v>759200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AH102" s="3">
         <v>-670400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AI102" s="3">
         <v>-710700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AJ102" s="3">
         <v>798800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AK102" s="3">
         <v>424100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AL102" s="3">
         <v>-166800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AM102" s="3">
         <v>1487500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AN102" s="3">
         <v>874100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AO102" s="3">
         <v>-181900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AP102" s="3">
         <v>1061400</v>
       </c>
     </row>
